--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192601</v>
+        <v>130192599</v>
       </c>
       <c r="B8" t="n">
-        <v>98809</v>
+        <v>98853</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>692070</v>
+        <v>692071</v>
       </c>
       <c r="R8" t="n">
-        <v>6667220</v>
+        <v>6667205</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130192600</v>
+        <v>130192601</v>
       </c>
       <c r="B9" t="n">
-        <v>101020</v>
+        <v>98809</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692095</v>
+        <v>692070</v>
       </c>
       <c r="R9" t="n">
-        <v>6667219</v>
+        <v>6667220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130192599</v>
+        <v>130192600</v>
       </c>
       <c r="B10" t="n">
-        <v>98853</v>
+        <v>101020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692071</v>
+        <v>692095</v>
       </c>
       <c r="R10" t="n">
-        <v>6667205</v>
+        <v>6667219</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130192594</v>
+        <v>130192596</v>
       </c>
       <c r="B13" t="n">
-        <v>104302</v>
+        <v>98809</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>692048</v>
       </c>
       <c r="R13" t="n">
-        <v>6667193</v>
+        <v>6667197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130192596</v>
+        <v>130192594</v>
       </c>
       <c r="B14" t="n">
-        <v>98809</v>
+        <v>104302</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
         <v>692048</v>
       </c>
       <c r="R14" t="n">
-        <v>6667197</v>
+        <v>6667193</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192599</v>
+        <v>130192601</v>
       </c>
       <c r="B8" t="n">
-        <v>98853</v>
+        <v>98809</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>692071</v>
+        <v>692070</v>
       </c>
       <c r="R8" t="n">
-        <v>6667205</v>
+        <v>6667220</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130192601</v>
+        <v>130192600</v>
       </c>
       <c r="B9" t="n">
-        <v>98809</v>
+        <v>101020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692070</v>
+        <v>692095</v>
       </c>
       <c r="R9" t="n">
-        <v>6667220</v>
+        <v>6667219</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130192600</v>
+        <v>130192599</v>
       </c>
       <c r="B10" t="n">
-        <v>101020</v>
+        <v>98853</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692095</v>
+        <v>692071</v>
       </c>
       <c r="R10" t="n">
-        <v>6667219</v>
+        <v>6667205</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130192596</v>
+        <v>130192594</v>
       </c>
       <c r="B13" t="n">
-        <v>98809</v>
+        <v>104302</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>692048</v>
       </c>
       <c r="R13" t="n">
-        <v>6667197</v>
+        <v>6667193</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130192594</v>
+        <v>130192596</v>
       </c>
       <c r="B14" t="n">
-        <v>104302</v>
+        <v>98809</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
         <v>692048</v>
       </c>
       <c r="R14" t="n">
-        <v>6667193</v>
+        <v>6667197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130192592</v>
       </c>
       <c r="B3" t="n">
-        <v>110987</v>
+        <v>110990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130192593</v>
       </c>
       <c r="B4" t="n">
-        <v>98809</v>
+        <v>98811</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130192606</v>
       </c>
       <c r="B5" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130192603</v>
       </c>
       <c r="B6" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130192597</v>
       </c>
       <c r="B7" t="n">
-        <v>98853</v>
+        <v>98855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>130192601</v>
       </c>
       <c r="B8" t="n">
-        <v>98809</v>
+        <v>98811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130192600</v>
+        <v>130192599</v>
       </c>
       <c r="B9" t="n">
-        <v>101020</v>
+        <v>98855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692095</v>
+        <v>692071</v>
       </c>
       <c r="R9" t="n">
-        <v>6667219</v>
+        <v>6667205</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130192599</v>
+        <v>130192600</v>
       </c>
       <c r="B10" t="n">
-        <v>98853</v>
+        <v>101022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692071</v>
+        <v>692095</v>
       </c>
       <c r="R10" t="n">
-        <v>6667205</v>
+        <v>6667219</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1686,7 +1686,7 @@
         <v>130192591</v>
       </c>
       <c r="B11" t="n">
-        <v>110987</v>
+        <v>110990</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130192602</v>
       </c>
       <c r="B12" t="n">
-        <v>98809</v>
+        <v>98811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130192594</v>
+        <v>130192596</v>
       </c>
       <c r="B13" t="n">
-        <v>104302</v>
+        <v>98811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>692048</v>
       </c>
       <c r="R13" t="n">
-        <v>6667193</v>
+        <v>6667197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130192596</v>
+        <v>130192594</v>
       </c>
       <c r="B14" t="n">
-        <v>98809</v>
+        <v>104304</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
         <v>692048</v>
       </c>
       <c r="R14" t="n">
-        <v>6667197</v>
+        <v>6667193</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130192592</v>
       </c>
       <c r="B3" t="n">
-        <v>110990</v>
+        <v>111077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130192593</v>
       </c>
       <c r="B4" t="n">
-        <v>98811</v>
+        <v>98898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130192606</v>
       </c>
       <c r="B5" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130192603</v>
       </c>
       <c r="B6" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130192597</v>
       </c>
       <c r="B7" t="n">
-        <v>98855</v>
+        <v>98942</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>130192601</v>
       </c>
       <c r="B8" t="n">
-        <v>98811</v>
+        <v>98898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130192599</v>
+        <v>130192600</v>
       </c>
       <c r="B9" t="n">
-        <v>98855</v>
+        <v>101109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692071</v>
+        <v>692095</v>
       </c>
       <c r="R9" t="n">
-        <v>6667205</v>
+        <v>6667219</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130192600</v>
+        <v>130192599</v>
       </c>
       <c r="B10" t="n">
-        <v>101022</v>
+        <v>98942</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692095</v>
+        <v>692071</v>
       </c>
       <c r="R10" t="n">
-        <v>6667219</v>
+        <v>6667205</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1686,7 +1686,7 @@
         <v>130192591</v>
       </c>
       <c r="B11" t="n">
-        <v>110990</v>
+        <v>111077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130192602</v>
       </c>
       <c r="B12" t="n">
-        <v>98811</v>
+        <v>98898</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130192596</v>
+        <v>130192594</v>
       </c>
       <c r="B13" t="n">
-        <v>98811</v>
+        <v>104391</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>692048</v>
       </c>
       <c r="R13" t="n">
-        <v>6667197</v>
+        <v>6667193</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130192594</v>
+        <v>130192596</v>
       </c>
       <c r="B14" t="n">
-        <v>104304</v>
+        <v>98898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
         <v>692048</v>
       </c>
       <c r="R14" t="n">
-        <v>6667193</v>
+        <v>6667197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130192598</v>
+        <v>130192592</v>
       </c>
       <c r="B2" t="n">
-        <v>5197</v>
+        <v>111077</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>692069</v>
+        <v>692056</v>
       </c>
       <c r="R2" t="n">
-        <v>6667203</v>
+        <v>6667196</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130192592</v>
+        <v>130192598</v>
       </c>
       <c r="B3" t="n">
-        <v>111077</v>
+        <v>5197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692056</v>
+        <v>692069</v>
       </c>
       <c r="R3" t="n">
-        <v>6667196</v>
+        <v>6667203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130192592</v>
+        <v>130192598</v>
       </c>
       <c r="B2" t="n">
-        <v>111077</v>
+        <v>5197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>692056</v>
+        <v>692069</v>
       </c>
       <c r="R2" t="n">
-        <v>6667196</v>
+        <v>6667203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130192598</v>
+        <v>130192592</v>
       </c>
       <c r="B3" t="n">
-        <v>5197</v>
+        <v>111077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692069</v>
+        <v>692056</v>
       </c>
       <c r="R3" t="n">
-        <v>6667203</v>
+        <v>6667196</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130192596</v>
+        <v>130192594</v>
       </c>
       <c r="B13" t="n">
-        <v>98898</v>
+        <v>104391</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>692048</v>
       </c>
       <c r="R13" t="n">
-        <v>6667197</v>
+        <v>6667193</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130192594</v>
+        <v>130192596</v>
       </c>
       <c r="B14" t="n">
-        <v>104391</v>
+        <v>98898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
         <v>692048</v>
       </c>
       <c r="R14" t="n">
-        <v>6667193</v>
+        <v>6667197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130192592</v>
       </c>
       <c r="B3" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130192593</v>
       </c>
       <c r="B4" t="n">
-        <v>98898</v>
+        <v>98901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130192606</v>
       </c>
       <c r="B5" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130192603</v>
       </c>
       <c r="B6" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130192597</v>
       </c>
       <c r="B7" t="n">
-        <v>98942</v>
+        <v>98945</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192601</v>
+        <v>130192600</v>
       </c>
       <c r="B8" t="n">
-        <v>98898</v>
+        <v>101112</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>692070</v>
+        <v>692095</v>
       </c>
       <c r="R8" t="n">
-        <v>6667220</v>
+        <v>6667219</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130192599</v>
+        <v>130192601</v>
       </c>
       <c r="B9" t="n">
-        <v>98942</v>
+        <v>98901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692071</v>
+        <v>692070</v>
       </c>
       <c r="R9" t="n">
-        <v>6667205</v>
+        <v>6667220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130192600</v>
+        <v>130192599</v>
       </c>
       <c r="B10" t="n">
-        <v>101109</v>
+        <v>98945</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692095</v>
+        <v>692071</v>
       </c>
       <c r="R10" t="n">
-        <v>6667219</v>
+        <v>6667205</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1686,7 +1686,7 @@
         <v>130192591</v>
       </c>
       <c r="B11" t="n">
-        <v>111077</v>
+        <v>111080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130192602</v>
       </c>
       <c r="B12" t="n">
-        <v>98898</v>
+        <v>98901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130192594</v>
+        <v>130192596</v>
       </c>
       <c r="B13" t="n">
-        <v>104391</v>
+        <v>98901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>692048</v>
       </c>
       <c r="R13" t="n">
-        <v>6667193</v>
+        <v>6667197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130192596</v>
+        <v>130192594</v>
       </c>
       <c r="B14" t="n">
-        <v>98898</v>
+        <v>104394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
         <v>692048</v>
       </c>
       <c r="R14" t="n">
-        <v>6667197</v>
+        <v>6667193</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130192592</v>
       </c>
       <c r="B3" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130192593</v>
       </c>
       <c r="B4" t="n">
-        <v>98901</v>
+        <v>98927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130192606</v>
       </c>
       <c r="B5" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130192603</v>
       </c>
       <c r="B6" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130192597</v>
       </c>
       <c r="B7" t="n">
-        <v>98945</v>
+        <v>98971</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192600</v>
+        <v>130192601</v>
       </c>
       <c r="B8" t="n">
-        <v>101112</v>
+        <v>98927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>692095</v>
+        <v>692070</v>
       </c>
       <c r="R8" t="n">
-        <v>6667219</v>
+        <v>6667220</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130192601</v>
+        <v>130192599</v>
       </c>
       <c r="B9" t="n">
-        <v>98901</v>
+        <v>98971</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692070</v>
+        <v>692071</v>
       </c>
       <c r="R9" t="n">
-        <v>6667220</v>
+        <v>6667205</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130192599</v>
+        <v>130192600</v>
       </c>
       <c r="B10" t="n">
-        <v>98945</v>
+        <v>101138</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692071</v>
+        <v>692095</v>
       </c>
       <c r="R10" t="n">
-        <v>6667205</v>
+        <v>6667219</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1686,7 +1686,7 @@
         <v>130192591</v>
       </c>
       <c r="B11" t="n">
-        <v>111080</v>
+        <v>111106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130192602</v>
       </c>
       <c r="B12" t="n">
-        <v>98901</v>
+        <v>98927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130192596</v>
       </c>
       <c r="B13" t="n">
-        <v>98901</v>
+        <v>98927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>130192594</v>
       </c>
       <c r="B14" t="n">
-        <v>104394</v>
+        <v>104420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192601</v>
+        <v>130192600</v>
       </c>
       <c r="B8" t="n">
-        <v>98927</v>
+        <v>101138</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>692070</v>
+        <v>692095</v>
       </c>
       <c r="R8" t="n">
-        <v>6667220</v>
+        <v>6667219</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130192599</v>
+        <v>130192601</v>
       </c>
       <c r="B9" t="n">
-        <v>98971</v>
+        <v>98927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692071</v>
+        <v>692070</v>
       </c>
       <c r="R9" t="n">
-        <v>6667205</v>
+        <v>6667220</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130192600</v>
+        <v>130192599</v>
       </c>
       <c r="B10" t="n">
-        <v>101138</v>
+        <v>98971</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692095</v>
+        <v>692071</v>
       </c>
       <c r="R10" t="n">
-        <v>6667219</v>
+        <v>6667205</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130192596</v>
+        <v>130192594</v>
       </c>
       <c r="B13" t="n">
-        <v>98927</v>
+        <v>104420</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>692048</v>
       </c>
       <c r="R13" t="n">
-        <v>6667197</v>
+        <v>6667193</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130192594</v>
+        <v>130192596</v>
       </c>
       <c r="B14" t="n">
-        <v>104420</v>
+        <v>98927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
         <v>692048</v>
       </c>
       <c r="R14" t="n">
-        <v>6667193</v>
+        <v>6667197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130192598</v>
+        <v>130192592</v>
       </c>
       <c r="B2" t="n">
-        <v>5197</v>
+        <v>111107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>219711</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>692069</v>
+        <v>692056</v>
       </c>
       <c r="R2" t="n">
-        <v>6667203</v>
+        <v>6667196</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130192592</v>
+        <v>130192598</v>
       </c>
       <c r="B3" t="n">
-        <v>111106</v>
+        <v>5197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692056</v>
+        <v>692069</v>
       </c>
       <c r="R3" t="n">
-        <v>6667196</v>
+        <v>6667203</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -902,7 +902,7 @@
         <v>130192593</v>
       </c>
       <c r="B4" t="n">
-        <v>98927</v>
+        <v>98928</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130192606</v>
       </c>
       <c r="B5" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130192603</v>
       </c>
       <c r="B6" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130192597</v>
       </c>
       <c r="B7" t="n">
-        <v>98971</v>
+        <v>98972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192600</v>
+        <v>130192601</v>
       </c>
       <c r="B8" t="n">
-        <v>101138</v>
+        <v>98928</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>692095</v>
+        <v>692070</v>
       </c>
       <c r="R8" t="n">
-        <v>6667219</v>
+        <v>6667220</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130192601</v>
+        <v>130192599</v>
       </c>
       <c r="B9" t="n">
-        <v>98927</v>
+        <v>98972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692070</v>
+        <v>692071</v>
       </c>
       <c r="R9" t="n">
-        <v>6667220</v>
+        <v>6667205</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130192599</v>
+        <v>130192600</v>
       </c>
       <c r="B10" t="n">
-        <v>98971</v>
+        <v>101139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692071</v>
+        <v>692095</v>
       </c>
       <c r="R10" t="n">
-        <v>6667205</v>
+        <v>6667219</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1686,7 +1686,7 @@
         <v>130192591</v>
       </c>
       <c r="B11" t="n">
-        <v>111106</v>
+        <v>111107</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130192602</v>
       </c>
       <c r="B12" t="n">
-        <v>98927</v>
+        <v>98928</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130192594</v>
       </c>
       <c r="B13" t="n">
-        <v>104420</v>
+        <v>104421</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>130192596</v>
       </c>
       <c r="B14" t="n">
-        <v>98927</v>
+        <v>98928</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130192592</v>
+        <v>130192598</v>
       </c>
       <c r="B2" t="n">
-        <v>111107</v>
+        <v>5197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>692056</v>
+        <v>692069</v>
       </c>
       <c r="R2" t="n">
-        <v>6667196</v>
+        <v>6667203</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130192598</v>
+        <v>130192592</v>
       </c>
       <c r="B3" t="n">
-        <v>5197</v>
+        <v>111108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>219711</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692069</v>
+        <v>692056</v>
       </c>
       <c r="R3" t="n">
-        <v>6667203</v>
+        <v>6667196</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -902,7 +902,7 @@
         <v>130192593</v>
       </c>
       <c r="B4" t="n">
-        <v>98928</v>
+        <v>98929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130192606</v>
       </c>
       <c r="B5" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130192603</v>
       </c>
       <c r="B6" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130192597</v>
       </c>
       <c r="B7" t="n">
-        <v>98972</v>
+        <v>98973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>130192601</v>
       </c>
       <c r="B8" t="n">
-        <v>98928</v>
+        <v>98929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130192599</v>
       </c>
       <c r="B9" t="n">
-        <v>98972</v>
+        <v>98973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>130192600</v>
       </c>
       <c r="B10" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>130192591</v>
       </c>
       <c r="B11" t="n">
-        <v>111107</v>
+        <v>111108</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130192602</v>
       </c>
       <c r="B12" t="n">
-        <v>98928</v>
+        <v>98929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130192594</v>
       </c>
       <c r="B13" t="n">
-        <v>104421</v>
+        <v>104422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>130192596</v>
       </c>
       <c r="B14" t="n">
-        <v>98928</v>
+        <v>98929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130192592</v>
       </c>
       <c r="B3" t="n">
-        <v>111108</v>
+        <v>111110</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130192593</v>
       </c>
       <c r="B4" t="n">
-        <v>98929</v>
+        <v>98931</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130192606</v>
       </c>
       <c r="B5" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130192603</v>
       </c>
       <c r="B6" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130192597</v>
       </c>
       <c r="B7" t="n">
-        <v>98973</v>
+        <v>98975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>130192601</v>
       </c>
       <c r="B8" t="n">
-        <v>98929</v>
+        <v>98931</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130192599</v>
+        <v>130192600</v>
       </c>
       <c r="B9" t="n">
-        <v>98973</v>
+        <v>101142</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219862</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692071</v>
+        <v>692095</v>
       </c>
       <c r="R9" t="n">
-        <v>6667205</v>
+        <v>6667219</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130192600</v>
+        <v>130192599</v>
       </c>
       <c r="B10" t="n">
-        <v>101140</v>
+        <v>98975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692095</v>
+        <v>692071</v>
       </c>
       <c r="R10" t="n">
-        <v>6667219</v>
+        <v>6667205</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1686,7 +1686,7 @@
         <v>130192591</v>
       </c>
       <c r="B11" t="n">
-        <v>111108</v>
+        <v>111110</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130192602</v>
       </c>
       <c r="B12" t="n">
-        <v>98929</v>
+        <v>98931</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130192594</v>
+        <v>130192596</v>
       </c>
       <c r="B13" t="n">
-        <v>104422</v>
+        <v>98931</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>219798</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>692048</v>
       </c>
       <c r="R13" t="n">
-        <v>6667193</v>
+        <v>6667197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130192596</v>
+        <v>130192594</v>
       </c>
       <c r="B14" t="n">
-        <v>98929</v>
+        <v>104424</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2057,7 +2057,7 @@
         <v>692048</v>
       </c>
       <c r="R14" t="n">
-        <v>6667197</v>
+        <v>6667193</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130192592</v>
       </c>
       <c r="B3" t="n">
-        <v>111110</v>
+        <v>111114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130192593</v>
       </c>
       <c r="B4" t="n">
-        <v>98931</v>
+        <v>98935</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130192606</v>
       </c>
       <c r="B5" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130192603</v>
       </c>
       <c r="B6" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130192597</v>
       </c>
       <c r="B7" t="n">
-        <v>98975</v>
+        <v>98979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192601</v>
+        <v>130192599</v>
       </c>
       <c r="B8" t="n">
-        <v>98931</v>
+        <v>98979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>692070</v>
+        <v>692071</v>
       </c>
       <c r="R8" t="n">
-        <v>6667220</v>
+        <v>6667205</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1462,7 +1462,7 @@
         <v>130192600</v>
       </c>
       <c r="B9" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130192599</v>
+        <v>130192601</v>
       </c>
       <c r="B10" t="n">
-        <v>98975</v>
+        <v>98935</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692071</v>
+        <v>692070</v>
       </c>
       <c r="R10" t="n">
-        <v>6667205</v>
+        <v>6667220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1686,7 +1686,7 @@
         <v>130192591</v>
       </c>
       <c r="B11" t="n">
-        <v>111110</v>
+        <v>111114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130192602</v>
       </c>
       <c r="B12" t="n">
-        <v>98931</v>
+        <v>98935</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130192596</v>
       </c>
       <c r="B13" t="n">
-        <v>98931</v>
+        <v>98935</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>130192594</v>
       </c>
       <c r="B14" t="n">
-        <v>104424</v>
+        <v>104428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>130192598</v>
       </c>
       <c r="B2" t="n">
-        <v>5197</v>
+        <v>5199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,14 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130192592</v>
+        <v>130192591</v>
       </c>
       <c r="B3" t="n">
-        <v>111114</v>
+        <v>111389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>692056</v>
+        <v>692062</v>
       </c>
       <c r="R3" t="n">
-        <v>6667196</v>
+        <v>6667179</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -899,32 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130192593</v>
+        <v>130192592</v>
       </c>
       <c r="B4" t="n">
-        <v>98935</v>
+        <v>111389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>219711</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>692054</v>
+        <v>692056</v>
       </c>
       <c r="R4" t="n">
-        <v>6667198</v>
+        <v>6667196</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130192606</v>
+        <v>130192593</v>
       </c>
       <c r="B5" t="n">
-        <v>101146</v>
+        <v>99096</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>692035</v>
+        <v>692054</v>
       </c>
       <c r="R5" t="n">
-        <v>6667244</v>
+        <v>6667198</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130192603</v>
+        <v>130192596</v>
       </c>
       <c r="B6" t="n">
-        <v>101146</v>
+        <v>99096</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>219798</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>692047</v>
+        <v>692048</v>
       </c>
       <c r="R6" t="n">
-        <v>6667219</v>
+        <v>6667197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130192597</v>
+        <v>130192601</v>
       </c>
       <c r="B7" t="n">
-        <v>98979</v>
+        <v>99096</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>692047</v>
+        <v>692070</v>
       </c>
       <c r="R7" t="n">
-        <v>6667209</v>
+        <v>6667220</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130192599</v>
+        <v>130192602</v>
       </c>
       <c r="B8" t="n">
-        <v>98979</v>
+        <v>99096</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,21 +1358,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219862</v>
+        <v>219798</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>692071</v>
+        <v>692080</v>
       </c>
       <c r="R8" t="n">
-        <v>6667205</v>
+        <v>6667216</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130192600</v>
+        <v>130192597</v>
       </c>
       <c r="B9" t="n">
-        <v>101146</v>
+        <v>99141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,21 +1470,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>692095</v>
+        <v>692047</v>
       </c>
       <c r="R9" t="n">
-        <v>6667219</v>
+        <v>6667209</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130192601</v>
+        <v>130192599</v>
       </c>
       <c r="B10" t="n">
-        <v>98935</v>
+        <v>99141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,21 +1582,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219798</v>
+        <v>219862</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>692070</v>
+        <v>692071</v>
       </c>
       <c r="R10" t="n">
-        <v>6667220</v>
+        <v>6667205</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130192591</v>
+        <v>130192589</v>
       </c>
       <c r="B11" t="n">
-        <v>111114</v>
+        <v>99156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,21 +1694,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>219875</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>692062</v>
+        <v>692069</v>
       </c>
       <c r="R11" t="n">
-        <v>6667179</v>
+        <v>6667163</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130192602</v>
+        <v>130192594</v>
       </c>
       <c r="B12" t="n">
-        <v>98935</v>
+        <v>104627</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1806,21 +1806,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219798</v>
+        <v>222412</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>692080</v>
+        <v>692048</v>
       </c>
       <c r="R12" t="n">
-        <v>6667216</v>
+        <v>6667193</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130192596</v>
+        <v>130192600</v>
       </c>
       <c r="B13" t="n">
-        <v>98935</v>
+        <v>101325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,21 +1918,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219798</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>692048</v>
+        <v>692095</v>
       </c>
       <c r="R13" t="n">
-        <v>6667197</v>
+        <v>6667219</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130192594</v>
+        <v>130192603</v>
       </c>
       <c r="B14" t="n">
-        <v>104428</v>
+        <v>101325</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2030,21 +2030,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2054,10 +2054,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>692048</v>
+        <v>692047</v>
       </c>
       <c r="R14" t="n">
-        <v>6667193</v>
+        <v>6667219</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2128,6 +2128,118 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130192606</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Östhammar, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>692035</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6667244</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Harg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>NVI (C250181) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46785-2023 artfynd.xlsx
+++ b/artfynd/A 46785-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192598</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192591</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192592</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192593</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192596</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192601</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192602</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192597</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192599</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192589</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1904,6 +1959,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192594</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2016,6 +2076,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192600</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2128,6 +2193,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192603</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2240,8 +2310,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130192606</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>